--- a/KURIKULUM2026_REVISI/012_ANALISIS_KRITIS_JALUR_PONDASI_DAN_TREE_PRASYARAT.xlsx
+++ b/KURIKULUM2026_REVISI/012_ANALISIS_KRITIS_JALUR_PONDASI_DAN_TREE_PRASYARAT.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>`STI-624`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>`STI-625`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>`STI-626`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>`STI-627`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>`STI-627` Platform, `MKU-204` KWU</t>
+          <t>`STI-727` Platform, `MKU-204` KWU</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>`STI-626` DL, `STI-417` Cloud</t>
+          <t>`STI-726` DL, `STI-417` Cloud</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>`STI-414` NLP &amp; IR, `STI-626` DL</t>
+          <t>`STI-414` NLP &amp; IR, `STI-726` DL</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>`STI-624` Integrasi Layanan Cerdas AI</t>
+          <t>`STI-726` Integrasi Layanan Cerdas AI</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>`STI-626` DL, `STI-521` IoT</t>
+          <t>`STI-726` DL, `STI-521` IoT</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>`STI-627` Platform, `STI-417` Cloud</t>
+          <t>`STI-727` Platform, `STI-417` Cloud</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
